--- a/data_src/articulos_revisados.xlsx
+++ b/data_src/articulos_revisados.xlsx
@@ -137,7 +137,7 @@
     <t>AR, GAME, ASD</t>
   </si>
   <si>
-    <t>sensor, feedback</t>
+    <t>body movement</t>
   </si>
   <si>
     <t>10.1016/j.ijcci.2024.100683</t>
@@ -222,9 +222,6 @@
   </si>
   <si>
     <t>Among various technological advances today, one of them is IoT (Internet of Things) which has been widely used in everyday life. IoT can make everything around us connected to the internet. At the same time, Augmented Reality is a technology that can combine three-dimensional virtual objects into the environment or the real world so that these objects appear more authentic. The two technologies can be integrated, which will then be applied in the game for autistic child therapy. The IoT-based technology used in this study is RFID (Radio Frequency Identification). Utilizing the RFID card, which will later be modified into a picture card in the game for autistic child therapy, is expected to help autistic children train their sensory and motor skills and interact with the characters in the game's three-dimensional form. Based on the results of the overall percentage of the learnability questionnaire, it can be concluded that 87.5% of respondents strongly agree, the results of the percentage of the overall efficiency questionnaire can be concluded that 84.67% of respondents strongly agree, then on the results of the percentage of the questionnaire memorability overall, it can be concluded that 82.22% of respondents strongly agree and the results of the percentage of satisfaction questionnaires as a whole, it can be concluded that 88.89% of respondents strongly agree. © 2024 American Institute of Physics Inc.. All rights reserved.</t>
-  </si>
-  <si>
-    <t>body movement</t>
   </si>
   <si>
     <t>10.1109/SeGAH61285.2024.10639571</t>
@@ -1112,6 +1109,9 @@
   </si>
   <si>
     <t>neuro</t>
+  </si>
+  <si>
+    <t>sensor, feedback</t>
   </si>
   <si>
     <t>eye, gaze,</t>
@@ -1772,7 +1772,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1787,6 +1787,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -2303,7 +2306,7 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="7" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2531,18 +2534,18 @@
         <v>0</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>46</v>
@@ -2567,13 +2570,13 @@
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>46</v>
@@ -2600,13 +2603,13 @@
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>46</v>
@@ -2628,18 +2631,18 @@
         <v>0</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>28</v>
@@ -2666,13 +2669,13 @@
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>28</v>
@@ -2699,16 +2702,16 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="E21" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2732,16 +2735,16 @@
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="E22" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2765,16 +2768,16 @@
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="E23" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2796,13 +2799,13 @@
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>36</v>
@@ -2827,10 +2830,10 @@
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>45</v>
@@ -2860,13 +2863,13 @@
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>28</v>
@@ -2891,13 +2894,13 @@
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>28</v>
@@ -2924,13 +2927,13 @@
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>16</v>
@@ -2952,18 +2955,18 @@
         <v>0</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>16</v>
@@ -2985,21 +2988,21 @@
         <v>0</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="E30" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3021,13 +3024,13 @@
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>119</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>28</v>
@@ -3049,18 +3052,18 @@
         <v>0</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>46</v>
@@ -3085,13 +3088,13 @@
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>125</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>46</v>
@@ -3116,13 +3119,13 @@
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>16</v>
@@ -3147,49 +3150,49 @@
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="E35" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>VR</v>
+      </c>
+      <c r="F35" s="4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G35" s="4">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H35" s="4">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="I35" s="4" t="s">
         <v>132</v>
-      </c>
-      <c r="E35" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>VR</v>
-      </c>
-      <c r="F35" s="4">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G35" s="4">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H35" s="4">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="D36" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E36" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3213,13 +3216,13 @@
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>46</v>
@@ -3244,13 +3247,13 @@
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>16</v>
@@ -3272,18 +3275,18 @@
         <v>0</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>16</v>
@@ -3308,13 +3311,13 @@
     </row>
     <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>16</v>
@@ -3335,19 +3338,19 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I40" s="7" t="s">
+      <c r="I40" s="8" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>16</v>
@@ -3374,13 +3377,13 @@
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>155</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>16</v>
@@ -3405,13 +3408,13 @@
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>158</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>28</v>
@@ -3438,13 +3441,13 @@
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>28</v>
@@ -3471,13 +3474,13 @@
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>164</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>28</v>
@@ -3499,21 +3502,21 @@
         <v>0</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="D46" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>168</v>
       </c>
       <c r="E46" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3535,13 +3538,13 @@
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>171</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>16</v>
@@ -3568,17 +3571,17 @@
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="D48" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="E48" s="3" t="str">
         <f t="shared" si="1"/>
         <v>VR</v>
@@ -3596,21 +3599,21 @@
         <v>0</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="D49" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E49" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3634,16 +3637,16 @@
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="D50" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E50" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3665,16 +3668,16 @@
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="D51" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>185</v>
       </c>
       <c r="E51" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3698,13 +3701,13 @@
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>188</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>16</v>
@@ -3731,16 +3734,16 @@
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="D53" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E53" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3762,13 +3765,13 @@
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>194</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>16</v>
@@ -3795,13 +3798,13 @@
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>46</v>
@@ -3828,11 +3831,11 @@
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B56" s="3"/>
       <c r="C56" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>16</v>
@@ -3857,16 +3860,16 @@
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="C57" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="D57" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="E57" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3890,42 +3893,42 @@
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B58" s="3"/>
       <c r="C58" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="E58" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>VR</v>
+      </c>
+      <c r="F58" s="4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G58" s="4">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H58" s="4">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="I58" s="4" t="s">
         <v>206</v>
-      </c>
-      <c r="E58" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>VR</v>
-      </c>
-      <c r="F58" s="4">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G58" s="4">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H58" s="4">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="I58" s="4" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B59" s="3"/>
       <c r="C59" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>16</v>
@@ -3950,14 +3953,14 @@
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B60" s="3"/>
       <c r="C60" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>211</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="E60" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3981,15 +3984,15 @@
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B61" s="3"/>
       <c r="C61" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D61" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="E61" s="3" t="str">
         <f t="shared" si="1"/>
         <v>VR</v>
@@ -4007,18 +4010,18 @@
         <v>1</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>218</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>62</v>
@@ -4045,49 +4048,49 @@
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="D63" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E63" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>VR</v>
+      </c>
+      <c r="F63" s="4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G63" s="4">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H63" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I63" s="4" t="s">
         <v>221</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E63" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>VR</v>
-      </c>
-      <c r="F63" s="4">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G63" s="4">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H63" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I63" s="4" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="C64" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="D64" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>226</v>
       </c>
       <c r="E64" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4109,13 +4112,13 @@
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="C65" s="3" t="s">
         <v>228</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>229</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>41</v>
@@ -4140,16 +4143,16 @@
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>232</v>
-      </c>
       <c r="D66" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E66" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4173,16 +4176,16 @@
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="C67" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="D67" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>236</v>
       </c>
       <c r="E67" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4206,17 +4209,17 @@
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="C68" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="D68" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>240</v>
-      </c>
       <c r="E68" s="3" t="str">
         <f t="shared" si="1"/>
         <v>AR</v>
@@ -4234,21 +4237,21 @@
         <v>0</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="C69" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="D69" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>244</v>
       </c>
       <c r="E69" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4270,16 +4273,16 @@
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="D70" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>248</v>
       </c>
       <c r="E70" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4303,16 +4306,16 @@
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="D71" s="3" t="s">
         <v>251</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>252</v>
       </c>
       <c r="E71" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4334,16 +4337,16 @@
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="C72" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="D72" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="E72" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4365,16 +4368,16 @@
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="D73" s="4" t="s">
         <v>259</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>260</v>
       </c>
       <c r="E73" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4396,16 +4399,16 @@
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="C74" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="D74" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="E74" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4427,13 +4430,13 @@
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="C75" s="3" t="s">
         <v>266</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>267</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>62</v>
@@ -4460,13 +4463,13 @@
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="C76" s="3" t="s">
         <v>269</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>270</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>62</v>
@@ -4491,16 +4494,16 @@
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B77" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="C77" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="D77" s="3" t="s">
         <v>273</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>274</v>
       </c>
       <c r="E77" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4522,16 +4525,16 @@
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="C78" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="D78" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>278</v>
       </c>
       <c r="E78" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4553,16 +4556,16 @@
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="D79" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>282</v>
       </c>
       <c r="E79" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4586,13 +4589,13 @@
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B80" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="C80" s="3" t="s">
         <v>284</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>285</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>36</v>
@@ -4617,16 +4620,16 @@
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="C81" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="C81" s="3" t="s">
-        <v>288</v>
-      </c>
       <c r="D81" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E81" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4650,13 +4653,13 @@
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="C82" s="3" t="s">
         <v>290</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>291</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>36</v>
@@ -4683,16 +4686,16 @@
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="C83" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="D83" s="3" t="s">
         <v>294</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>295</v>
       </c>
       <c r="E83" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4714,13 +4717,13 @@
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B84" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="C84" s="3" t="s">
         <v>297</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>298</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>62</v>
@@ -4745,13 +4748,13 @@
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="C85" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>62</v>
@@ -4773,142 +4776,142 @@
         <v>0</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
-      <c r="A86" s="8" t="s">
+      <c r="A86" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="B86" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="B86" s="8" t="s">
+      <c r="C86" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="C86" s="8" t="s">
+      <c r="D86" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E86" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>VR</v>
+      </c>
+      <c r="F86" s="4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G86" s="4">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H86" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I86" s="3"/>
+    </row>
+    <row r="87" ht="14.25" customHeight="1">
+      <c r="A87" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="D86" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E86" s="3" t="str">
+      <c r="B87" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E87" s="3" t="str">
         <f t="shared" si="1"/>
         <v>VR</v>
       </c>
-      <c r="F86" s="4">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G86" s="4">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H86" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I86" s="3"/>
-    </row>
-    <row r="87" ht="14.25" customHeight="1">
-      <c r="A87" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="B87" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="C87" s="8" t="s">
+      <c r="F87" s="4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G87" s="4">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H87" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I87" s="3"/>
+    </row>
+    <row r="88" ht="14.25" customHeight="1">
+      <c r="A88" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="D87" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E87" s="3" t="str">
+      <c r="B88" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="E88" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>AR</v>
+      </c>
+      <c r="F88" s="4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G88" s="4">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H88" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I88" s="3"/>
+    </row>
+    <row r="89" ht="14.25" customHeight="1">
+      <c r="A89" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E89" s="3" t="str">
         <f t="shared" si="1"/>
         <v>VR</v>
       </c>
-      <c r="F87" s="4">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G87" s="4">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H87" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I87" s="3"/>
-    </row>
-    <row r="88" ht="14.25" customHeight="1">
-      <c r="A88" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="B88" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="E88" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>AR</v>
-      </c>
-      <c r="F88" s="4">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G88" s="4">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H88" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I88" s="3"/>
-    </row>
-    <row r="89" ht="14.25" customHeight="1">
-      <c r="A89" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="B89" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="C89" s="8" t="s">
+      <c r="F89" s="4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G89" s="4">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H89" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I89" s="3"/>
+    </row>
+    <row r="90" ht="14.25" customHeight="1">
+      <c r="A90" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E89" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>VR</v>
-      </c>
-      <c r="F89" s="4">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G89" s="4">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H89" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I89" s="3"/>
-    </row>
-    <row r="90" ht="14.25" customHeight="1">
-      <c r="A90" s="8" t="s">
+      <c r="B90" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="B90" s="9" t="s">
+      <c r="C90" s="9" t="s">
         <v>316</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>317</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>62</v>
@@ -4932,78 +4935,78 @@
       <c r="I90" s="3"/>
     </row>
     <row r="91" ht="14.25" customHeight="1">
-      <c r="A91" s="8" t="s">
+      <c r="A91" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="B91" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="B91" s="9" t="s">
+      <c r="C91" s="9" t="s">
         <v>319</v>
       </c>
-      <c r="C91" s="8" t="s">
+      <c r="D91" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E91" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>VR</v>
+      </c>
+      <c r="F91" s="4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G91" s="4">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H91" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I91" s="3"/>
+    </row>
+    <row r="92" ht="14.25" customHeight="1">
+      <c r="A92" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="D91" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="E91" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>VR</v>
-      </c>
-      <c r="F91" s="4">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G91" s="4">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H91" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I91" s="3"/>
-    </row>
-    <row r="92" ht="14.25" customHeight="1">
-      <c r="A92" s="8" t="s">
+      <c r="B92" s="9" t="s">
         <v>321</v>
       </c>
-      <c r="B92" s="8" t="s">
+      <c r="C92" s="9" t="s">
         <v>322</v>
       </c>
-      <c r="C92" s="8" t="s">
+      <c r="D92" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="D92" s="4" t="s">
+      <c r="E92" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>MR</v>
+      </c>
+      <c r="F92" s="4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G92" s="4">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H92" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I92" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="E92" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>MR</v>
-      </c>
-      <c r="F92" s="4">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G92" s="4">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H92" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I92" s="3" t="s">
+    </row>
+    <row r="93" ht="14.25" customHeight="1">
+      <c r="A93" s="9" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="93" ht="14.25" customHeight="1">
-      <c r="A93" s="8" t="s">
+      <c r="B93" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="B93" s="8" t="s">
+      <c r="C93" s="9" t="s">
         <v>327</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>328</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>62</v>
@@ -5029,47 +5032,47 @@
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
-      <c r="A94" s="8" t="s">
+      <c r="A94" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="B94" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="B94" s="8" t="s">
+      <c r="C94" s="9" t="s">
         <v>330</v>
       </c>
-      <c r="C94" s="8" t="s">
+      <c r="D94" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E94" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>VR</v>
+      </c>
+      <c r="F94" s="4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G94" s="4">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H94" s="4">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="I94" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="95" ht="14.25" customHeight="1">
+      <c r="A95" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="D94" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E94" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>VR</v>
-      </c>
-      <c r="F94" s="4">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G94" s="4">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H94" s="4">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="I94" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="95" ht="14.25" customHeight="1">
-      <c r="A95" s="8" t="s">
+      <c r="B95" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="B95" s="8" t="s">
+      <c r="C95" s="9" t="s">
         <v>333</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>334</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>62</v>
@@ -5093,14 +5096,14 @@
       <c r="I95" s="3"/>
     </row>
     <row r="96" ht="14.25" customHeight="1">
-      <c r="A96" s="8" t="s">
+      <c r="A96" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="B96" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="B96" s="8" t="s">
+      <c r="C96" s="9" t="s">
         <v>336</v>
-      </c>
-      <c r="C96" s="8" t="s">
-        <v>337</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>62</v>
@@ -5126,14 +5129,14 @@
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
-      <c r="A97" s="8" t="s">
+      <c r="A97" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="B97" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="B97" s="8" t="s">
+      <c r="C97" s="9" t="s">
         <v>339</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>340</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>62</v>
@@ -5159,14 +5162,14 @@
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
-      <c r="A98" s="8" t="s">
+      <c r="A98" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="B98" s="9" t="s">
         <v>341</v>
       </c>
-      <c r="B98" s="8" t="s">
+      <c r="C98" s="9" t="s">
         <v>342</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>343</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>62</v>
@@ -5188,18 +5191,18 @@
         <v>0</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
-      <c r="A99" s="8" t="s">
+      <c r="A99" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="B99" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="B99" s="8" t="s">
+      <c r="C99" s="9" t="s">
         <v>345</v>
-      </c>
-      <c r="C99" s="8" t="s">
-        <v>346</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>62</v>
@@ -5223,17 +5226,17 @@
       <c r="I99" s="3"/>
     </row>
     <row r="100" ht="14.25" customHeight="1">
-      <c r="A100" s="8" t="s">
+      <c r="A100" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="B100" s="9" t="s">
         <v>347</v>
       </c>
-      <c r="B100" s="8" t="s">
+      <c r="C100" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="C100" s="8" t="s">
+      <c r="D100" s="3" t="s">
         <v>349</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>350</v>
       </c>
       <c r="E100" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6154,7 +6157,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
@@ -6204,7 +6207,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
@@ -6268,7 +6271,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
@@ -6301,7 +6304,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
@@ -6365,7 +6368,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
@@ -6398,7 +6401,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>37</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
@@ -6497,7 +6500,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
@@ -6630,13 +6633,13 @@
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>46</v>
@@ -6661,13 +6664,13 @@
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>46</v>
@@ -6694,13 +6697,13 @@
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>46</v>
@@ -6727,13 +6730,13 @@
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>28</v>
@@ -6760,13 +6763,13 @@
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>28</v>
@@ -6793,16 +6796,16 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="E21" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6826,16 +6829,16 @@
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="E22" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6859,16 +6862,16 @@
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="E23" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6890,13 +6893,13 @@
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>36</v>
@@ -6921,10 +6924,10 @@
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>365</v>
@@ -6954,13 +6957,13 @@
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>28</v>
@@ -6985,13 +6988,13 @@
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>28</v>
@@ -7018,13 +7021,13 @@
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>16</v>
@@ -7051,13 +7054,13 @@
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>16</v>
@@ -7084,16 +7087,16 @@
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="E30" s="3" t="str">
         <f t="shared" si="1"/>
@@ -7115,13 +7118,13 @@
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>119</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>28</v>
@@ -7148,13 +7151,13 @@
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>46</v>
@@ -7179,13 +7182,13 @@
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>125</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>46</v>
@@ -7210,13 +7213,13 @@
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>16</v>
@@ -7241,16 +7244,16 @@
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="E35" s="3" t="str">
         <f t="shared" si="1"/>
@@ -7274,16 +7277,16 @@
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="D36" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E36" s="3" t="str">
         <f t="shared" si="1"/>
@@ -7307,13 +7310,13 @@
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>46</v>
@@ -7338,13 +7341,13 @@
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>16</v>
@@ -7371,13 +7374,13 @@
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>16</v>
@@ -7402,13 +7405,13 @@
     </row>
     <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>16</v>
@@ -7429,19 +7432,19 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I40" s="7" t="s">
+      <c r="I40" s="8" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>16</v>
@@ -7468,13 +7471,13 @@
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>155</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>16</v>
@@ -7499,13 +7502,13 @@
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>158</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>28</v>
@@ -7526,19 +7529,19 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I43" s="10" t="s">
+      <c r="I43" s="11" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>28</v>
@@ -7565,13 +7568,13 @@
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>164</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>28</v>
@@ -7598,16 +7601,16 @@
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="D46" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>168</v>
       </c>
       <c r="E46" s="3" t="str">
         <f t="shared" si="1"/>
@@ -7629,13 +7632,13 @@
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>171</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>16</v>
@@ -7662,16 +7665,16 @@
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="D48" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>175</v>
       </c>
       <c r="E48" s="3" t="str">
         <f t="shared" si="1"/>
@@ -7695,16 +7698,16 @@
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="D49" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E49" s="3" t="str">
         <f t="shared" si="1"/>
@@ -7728,16 +7731,16 @@
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="D50" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E50" s="3" t="str">
         <f t="shared" si="1"/>
@@ -7759,16 +7762,16 @@
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="D51" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>185</v>
       </c>
       <c r="E51" s="3" t="str">
         <f t="shared" si="1"/>
@@ -7792,13 +7795,13 @@
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>188</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>16</v>
@@ -7825,16 +7828,16 @@
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="D53" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E53" s="3" t="str">
         <f t="shared" si="1"/>
@@ -7856,13 +7859,13 @@
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>194</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>16</v>
@@ -7889,13 +7892,13 @@
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>46</v>
@@ -7922,11 +7925,11 @@
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B56" s="3"/>
       <c r="C56" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>16</v>
@@ -7951,17 +7954,17 @@
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="C57" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="D57" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="D57" s="4" t="s">
-        <v>203</v>
-      </c>
       <c r="E57" s="3" t="str">
         <f t="shared" si="1"/>
         <v>VR, AR</v>
@@ -7979,19 +7982,19 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B58" s="3"/>
       <c r="C58" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>205</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>206</v>
       </c>
       <c r="E58" s="3" t="str">
         <f t="shared" si="1"/>
@@ -8015,11 +8018,11 @@
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B59" s="3"/>
       <c r="C59" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>16</v>
@@ -8044,14 +8047,14 @@
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B60" s="3"/>
       <c r="C60" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>211</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="E60" s="3" t="str">
         <f t="shared" si="1"/>
@@ -8075,14 +8078,14 @@
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B61" s="3"/>
       <c r="C61" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D61" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>215</v>
       </c>
       <c r="E61" s="3" t="str">
         <f t="shared" si="1"/>
@@ -8106,13 +8109,13 @@
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>218</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>62</v>
@@ -8134,21 +8137,21 @@
         <v>0</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C63" s="3" t="s">
-        <v>221</v>
-      </c>
       <c r="D63" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E63" s="3" t="str">
         <f t="shared" si="1"/>
@@ -8172,16 +8175,16 @@
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="C64" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="D64" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>226</v>
       </c>
       <c r="E64" s="3" t="str">
         <f t="shared" si="1"/>
@@ -8203,13 +8206,13 @@
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="C65" s="3" t="s">
         <v>228</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>229</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>41</v>
@@ -8234,16 +8237,16 @@
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>232</v>
-      </c>
       <c r="D66" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E66" s="3" t="str">
         <f t="shared" si="1"/>
@@ -8267,17 +8270,17 @@
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="C67" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="D67" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>236</v>
-      </c>
       <c r="E67" s="3" t="str">
         <f t="shared" si="1"/>
         <v>VR</v>
@@ -8295,21 +8298,21 @@
         <v>0</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="C68" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="D68" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>240</v>
       </c>
       <c r="E68" s="3" t="str">
         <f t="shared" si="1"/>
@@ -8333,16 +8336,16 @@
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="C69" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="D69" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>244</v>
       </c>
       <c r="E69" s="3" t="str">
         <f t="shared" si="1"/>
@@ -8364,16 +8367,16 @@
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="D70" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>248</v>
       </c>
       <c r="E70" s="3" t="str">
         <f t="shared" si="1"/>
@@ -8397,16 +8400,16 @@
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="D71" s="3" t="s">
         <v>251</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>252</v>
       </c>
       <c r="E71" s="3" t="str">
         <f t="shared" si="1"/>
@@ -8428,16 +8431,16 @@
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="C72" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="D72" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="E72" s="3" t="str">
         <f t="shared" si="1"/>
@@ -8459,16 +8462,16 @@
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="D73" s="4" t="s">
         <v>259</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>260</v>
       </c>
       <c r="E73" s="3" t="str">
         <f t="shared" si="1"/>
@@ -8490,16 +8493,16 @@
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="C74" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="D74" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="E74" s="3" t="str">
         <f t="shared" si="1"/>
@@ -8529,7 +8532,7 @@
       <c r="C75" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="D75" s="11" t="s">
+      <c r="D75" s="12" t="s">
         <v>389</v>
       </c>
       <c r="E75" s="3" t="str">
@@ -8552,13 +8555,13 @@
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="C76" s="3" t="s">
         <v>266</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>267</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>62</v>
@@ -8585,13 +8588,13 @@
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B77" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="C77" s="3" t="s">
         <v>269</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>270</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>62</v>
@@ -8616,16 +8619,16 @@
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="C78" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="D78" s="3" t="s">
         <v>273</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>274</v>
       </c>
       <c r="E78" s="3" t="str">
         <f t="shared" si="1"/>
@@ -8647,16 +8650,16 @@
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="D79" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>278</v>
       </c>
       <c r="E79" s="3" t="str">
         <f t="shared" si="1"/>
@@ -8678,13 +8681,13 @@
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B80" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="C80" s="3" t="s">
         <v>280</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>281</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>36</v>
@@ -8711,13 +8714,13 @@
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="C81" s="3" t="s">
         <v>284</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>285</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>36</v>
@@ -8742,13 +8745,13 @@
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="C82" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>288</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>390</v>
@@ -8770,18 +8773,18 @@
         <v>0</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>37</v>
+        <v>355</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="C83" s="3" t="s">
         <v>290</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>291</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>36</v>
@@ -8816,7 +8819,7 @@
       <c r="C84" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="D84" s="11" t="s">
+      <c r="D84" s="12" t="s">
         <v>395</v>
       </c>
       <c r="E84" s="3" t="str">
@@ -8841,16 +8844,16 @@
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="C85" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="D85" s="3" t="s">
         <v>294</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>295</v>
       </c>
       <c r="E85" s="3" t="str">
         <f t="shared" si="1"/>
@@ -8880,7 +8883,7 @@
       <c r="C86" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="D86" s="11" t="s">
+      <c r="D86" s="12" t="s">
         <v>395</v>
       </c>
       <c r="E86" s="3" t="str">
@@ -8905,13 +8908,13 @@
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B87" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="C87" s="3" t="s">
         <v>297</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>298</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>62</v>
@@ -8936,13 +8939,13 @@
     </row>
     <row r="88" ht="14.25" customHeight="1">
       <c r="A88" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="C88" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>62</v>
@@ -8977,7 +8980,7 @@
       <c r="C89" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="D89" s="11" t="s">
+      <c r="D89" s="12" t="s">
         <v>395</v>
       </c>
       <c r="E89" s="3" t="str">
@@ -9001,17 +9004,17 @@
       </c>
     </row>
     <row r="90" ht="14.25" customHeight="1">
-      <c r="A90" s="8" t="s">
+      <c r="A90" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="B90" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="C90" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="C90" s="8" t="s">
-        <v>304</v>
-      </c>
       <c r="D90" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E90" s="3" t="str">
         <f t="shared" si="1"/>
@@ -9034,169 +9037,169 @@
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
-      <c r="A91" s="8" t="s">
+      <c r="A91" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="B91" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="B91" s="8" t="s">
+      <c r="C91" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="C91" s="8" t="s">
+      <c r="D91" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E91" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>VR</v>
+      </c>
+      <c r="F91" s="4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G91" s="4">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H91" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I91" s="3"/>
+    </row>
+    <row r="92" ht="14.25" customHeight="1">
+      <c r="A92" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E92" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F92" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G92" s="4">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H92" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I92" s="3"/>
+    </row>
+    <row r="93" ht="14.25" customHeight="1">
+      <c r="A93" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E91" s="3" t="str">
+      <c r="B93" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="E93" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>AR</v>
+      </c>
+      <c r="F93" s="4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G93" s="4">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H93" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I93" s="3"/>
+    </row>
+    <row r="94" ht="14.25" customHeight="1">
+      <c r="A94" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="C94" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E94" s="3" t="str">
         <f t="shared" si="1"/>
         <v>VR</v>
       </c>
-      <c r="F91" s="4">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G91" s="4">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H91" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I91" s="3"/>
-    </row>
-    <row r="92" ht="14.25" customHeight="1">
-      <c r="A92" s="8" t="s">
-        <v>405</v>
-      </c>
-      <c r="B92" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>407</v>
-      </c>
-      <c r="D92" s="11" t="s">
+      <c r="F94" s="4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G94" s="4">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H94" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I94" s="3"/>
+    </row>
+    <row r="95" ht="14.25" customHeight="1">
+      <c r="A95" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="B95" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C95" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="D95" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E92" s="3" t="str">
+      <c r="E95" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F92" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G92" s="4">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H92" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I92" s="3"/>
-    </row>
-    <row r="93" ht="14.25" customHeight="1">
-      <c r="A93" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="B93" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="E93" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>AR</v>
-      </c>
-      <c r="F93" s="4">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G93" s="4">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H93" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I93" s="3"/>
-    </row>
-    <row r="94" ht="14.25" customHeight="1">
-      <c r="A94" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="B94" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="C94" s="8" t="s">
+      <c r="F95" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G95" s="4">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H95" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I95" s="3"/>
+    </row>
+    <row r="96" ht="14.25" customHeight="1">
+      <c r="A96" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E94" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>VR</v>
-      </c>
-      <c r="F94" s="4">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G94" s="4">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H94" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I94" s="3"/>
-    </row>
-    <row r="95" ht="14.25" customHeight="1">
-      <c r="A95" s="8" t="s">
-        <v>408</v>
-      </c>
-      <c r="B95" s="8" t="s">
-        <v>409</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>410</v>
-      </c>
-      <c r="D95" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E95" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F95" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G95" s="4">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H95" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I95" s="3"/>
-    </row>
-    <row r="96" ht="14.25" customHeight="1">
-      <c r="A96" s="8" t="s">
+      <c r="B96" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="B96" s="9" t="s">
+      <c r="C96" s="9" t="s">
         <v>316</v>
-      </c>
-      <c r="C96" s="8" t="s">
-        <v>317</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>62</v>
@@ -9220,17 +9223,17 @@
       <c r="I96" s="3"/>
     </row>
     <row r="97" ht="14.25" customHeight="1">
-      <c r="A97" s="8" t="s">
+      <c r="A97" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="B97" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="B97" s="9" t="s">
+      <c r="C97" s="9" t="s">
         <v>319</v>
       </c>
-      <c r="C97" s="8" t="s">
-        <v>320</v>
-      </c>
       <c r="D97" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E97" s="3" t="str">
         <f t="shared" si="1"/>
@@ -9251,14 +9254,14 @@
       <c r="I97" s="3"/>
     </row>
     <row r="98" ht="14.25" customHeight="1">
-      <c r="A98" s="8" t="s">
+      <c r="A98" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="B98" s="9"/>
-      <c r="C98" s="8" t="s">
+      <c r="B98" s="10"/>
+      <c r="C98" s="9" t="s">
         <v>412</v>
       </c>
-      <c r="D98" s="11" t="s">
+      <c r="D98" s="12" t="s">
         <v>6</v>
       </c>
       <c r="E98" s="3" t="str">
@@ -9282,16 +9285,16 @@
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
-      <c r="A99" s="9" t="s">
+      <c r="A99" s="10" t="s">
         <v>414</v>
       </c>
-      <c r="B99" s="8" t="s">
+      <c r="B99" s="9" t="s">
         <v>415</v>
       </c>
-      <c r="C99" s="8" t="s">
+      <c r="C99" s="9" t="s">
         <v>416</v>
       </c>
-      <c r="D99" s="11" t="s">
+      <c r="D99" s="12" t="s">
         <v>6</v>
       </c>
       <c r="E99" s="3" t="str">
@@ -9313,49 +9316,49 @@
       <c r="I99" s="3"/>
     </row>
     <row r="100" ht="14.25" customHeight="1">
-      <c r="A100" s="8" t="s">
+      <c r="A100" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="B100" s="9" t="s">
         <v>321</v>
       </c>
-      <c r="B100" s="8" t="s">
+      <c r="C100" s="9" t="s">
         <v>322</v>
       </c>
-      <c r="C100" s="8" t="s">
+      <c r="D100" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="D100" s="4" t="s">
+      <c r="E100" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>MR</v>
+      </c>
+      <c r="F100" s="4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G100" s="4">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H100" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I100" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="E100" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>MR</v>
-      </c>
-      <c r="F100" s="4">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G100" s="4">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H100" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>325</v>
-      </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
-      <c r="A101" s="8" t="s">
+      <c r="A101" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="B101" s="8" t="s">
+      <c r="B101" s="9" t="s">
         <v>418</v>
       </c>
-      <c r="C101" s="8" t="s">
+      <c r="C101" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="D101" s="12" t="s">
+      <c r="D101" s="13" t="s">
         <v>420</v>
       </c>
       <c r="E101" s="3" t="str">
@@ -9379,16 +9382,16 @@
       </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
-      <c r="A102" s="8" t="s">
+      <c r="A102" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="B102" s="8" t="s">
+      <c r="B102" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="C102" s="8" t="s">
+      <c r="C102" s="9" t="s">
         <v>424</v>
       </c>
-      <c r="D102" s="11" t="s">
+      <c r="D102" s="12" t="s">
         <v>5</v>
       </c>
       <c r="E102" s="3" t="str">
@@ -9410,16 +9413,16 @@
       <c r="I102" s="3"/>
     </row>
     <row r="103" ht="14.25" customHeight="1">
-      <c r="A103" s="8" t="s">
+      <c r="A103" s="9" t="s">
         <v>425</v>
       </c>
-      <c r="B103" s="8" t="s">
+      <c r="B103" s="9" t="s">
         <v>426</v>
       </c>
-      <c r="C103" s="8" t="s">
+      <c r="C103" s="9" t="s">
         <v>427</v>
       </c>
-      <c r="D103" s="12" t="s">
+      <c r="D103" s="13" t="s">
         <v>428</v>
       </c>
       <c r="E103" s="3" t="str">
@@ -9443,14 +9446,14 @@
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
-      <c r="A104" s="8" t="s">
+      <c r="A104" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="B104" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="B104" s="8" t="s">
+      <c r="C104" s="9" t="s">
         <v>327</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>328</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>62</v>
@@ -9472,18 +9475,18 @@
         <v>0</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="105" ht="14.25" customHeight="1">
-      <c r="A105" s="8" t="s">
+      <c r="A105" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="B105" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="B105" s="8" t="s">
+      <c r="C105" s="9" t="s">
         <v>330</v>
-      </c>
-      <c r="C105" s="8" t="s">
-        <v>331</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>46</v>
@@ -9505,18 +9508,18 @@
         <v>0</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
-      <c r="A106" s="8" t="s">
+      <c r="A106" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="B106" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="B106" s="8" t="s">
+      <c r="C106" s="9" t="s">
         <v>333</v>
-      </c>
-      <c r="C106" s="8" t="s">
-        <v>334</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>62</v>
@@ -9542,14 +9545,14 @@
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
-      <c r="A107" s="8" t="s">
+      <c r="A107" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="B107" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="B107" s="8" t="s">
+      <c r="C107" s="9" t="s">
         <v>336</v>
-      </c>
-      <c r="C107" s="8" t="s">
-        <v>337</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>62</v>
@@ -9575,14 +9578,14 @@
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
-      <c r="A108" s="8" t="s">
+      <c r="A108" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="B108" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="B108" s="8" t="s">
+      <c r="C108" s="9" t="s">
         <v>339</v>
-      </c>
-      <c r="C108" s="8" t="s">
-        <v>340</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>62</v>
@@ -9608,14 +9611,14 @@
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
-      <c r="A109" s="8" t="s">
+      <c r="A109" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="B109" s="9" t="s">
         <v>341</v>
       </c>
-      <c r="B109" s="8" t="s">
+      <c r="C109" s="9" t="s">
         <v>342</v>
-      </c>
-      <c r="C109" s="8" t="s">
-        <v>343</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>62</v>
@@ -9641,14 +9644,14 @@
       </c>
     </row>
     <row r="110" ht="14.25" customHeight="1">
-      <c r="A110" s="8" t="s">
+      <c r="A110" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="B110" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="B110" s="8" t="s">
+      <c r="C110" s="9" t="s">
         <v>345</v>
-      </c>
-      <c r="C110" s="8" t="s">
-        <v>346</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>62</v>
@@ -9672,17 +9675,17 @@
       <c r="I110" s="3"/>
     </row>
     <row r="111" ht="14.25" customHeight="1">
-      <c r="A111" s="8" t="s">
+      <c r="A111" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="B111" s="9" t="s">
         <v>347</v>
       </c>
-      <c r="B111" s="8" t="s">
+      <c r="C111" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="C111" s="8" t="s">
+      <c r="D111" s="3" t="s">
         <v>349</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>350</v>
       </c>
       <c r="E111" s="3" t="str">
         <f t="shared" si="1"/>
@@ -10619,7 +10622,7 @@
       <c r="H1" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>436</v>
       </c>
     </row>
@@ -10637,7 +10640,7 @@
         <v>12</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>437</v>
@@ -10649,7 +10652,7 @@
       <c r="I2" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="15" t="s">
         <v>440</v>
       </c>
     </row>
@@ -10675,7 +10678,7 @@
       <c r="I3" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="15" t="s">
         <v>440</v>
       </c>
     </row>
@@ -10693,7 +10696,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>443</v>
@@ -10701,7 +10704,7 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="15" t="s">
         <v>444</v>
       </c>
     </row>
@@ -10719,7 +10722,7 @@
         <v>16</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>441</v>
@@ -10731,7 +10734,7 @@
       <c r="I5" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="15" t="s">
         <v>440</v>
       </c>
     </row>
@@ -10759,7 +10762,7 @@
       <c r="I6" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="15" t="s">
         <v>440</v>
       </c>
     </row>
@@ -10777,7 +10780,7 @@
         <v>32</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>447</v>
@@ -10789,7 +10792,7 @@
       <c r="I7" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="J7" s="15" t="s">
         <v>440</v>
       </c>
     </row>
@@ -10807,7 +10810,7 @@
         <v>36</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>37</v>
+        <v>355</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>448</v>
@@ -10817,7 +10820,7 @@
       <c r="I8" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="J8" s="15" t="s">
         <v>440</v>
       </c>
     </row>
@@ -10887,7 +10890,7 @@
         <v>28</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>446</v>
@@ -10994,13 +10997,13 @@
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>46</v>
@@ -11015,13 +11018,13 @@
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>46</v>
@@ -11038,13 +11041,13 @@
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>46</v>
@@ -11071,7 +11074,7 @@
       <c r="C19" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="16" t="s">
         <v>455</v>
       </c>
       <c r="E19" s="3"/>
@@ -11088,13 +11091,13 @@
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>28</v>
@@ -11111,13 +11114,13 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>28</v>
@@ -11134,16 +11137,16 @@
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>363</v>
@@ -11157,16 +11160,16 @@
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>364</v>
@@ -11182,16 +11185,16 @@
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
@@ -11203,13 +11206,13 @@
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>36</v>
@@ -11224,10 +11227,10 @@
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>365</v>
@@ -11247,13 +11250,13 @@
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>28</v>
@@ -11270,13 +11273,13 @@
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>28</v>
@@ -11293,13 +11296,13 @@
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>16</v>
@@ -11318,13 +11321,13 @@
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>16</v>
@@ -11343,16 +11346,16 @@
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
@@ -11364,13 +11367,13 @@
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>119</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>28</v>
@@ -11387,13 +11390,13 @@
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>46</v>
@@ -11416,7 +11419,7 @@
       <c r="C34" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="D34" s="16" t="s">
+      <c r="D34" s="17" t="s">
         <v>5</v>
       </c>
       <c r="E34" s="3"/>
@@ -11429,13 +11432,13 @@
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>125</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>46</v>
@@ -11452,13 +11455,13 @@
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>16</v>
@@ -11470,20 +11473,20 @@
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
-      <c r="J36" s="17"/>
+      <c r="J36" s="18"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>368</v>
@@ -11499,16 +11502,16 @@
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="D38" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>369</v>
@@ -11524,13 +11527,13 @@
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>46</v>
@@ -11547,13 +11550,13 @@
     </row>
     <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>16</v>
@@ -11570,13 +11573,13 @@
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>16</v>
@@ -11593,18 +11596,18 @@
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="8" t="s">
         <v>371</v>
       </c>
       <c r="F42" s="3" t="s">
@@ -11616,13 +11619,13 @@
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>16</v>
@@ -11641,13 +11644,13 @@
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>155</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>16</v>
@@ -11662,18 +11665,18 @@
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>158</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="E45" s="11" t="s">
         <v>372</v>
       </c>
       <c r="F45" s="3" t="s">
@@ -11685,13 +11688,13 @@
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>466</v>
@@ -11716,7 +11719,7 @@
       <c r="C47" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="D47" s="15" t="s">
+      <c r="D47" s="16" t="s">
         <v>470</v>
       </c>
       <c r="E47" s="3" t="s">
@@ -11733,13 +11736,13 @@
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>164</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>28</v>
@@ -11758,16 +11761,16 @@
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="D49" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>168</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3" t="s">
@@ -11783,13 +11786,13 @@
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>171</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>16</v>
@@ -11808,16 +11811,16 @@
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="D51" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>175</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>372</v>
@@ -11831,16 +11834,16 @@
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="D52" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>376</v>
@@ -11854,16 +11857,16 @@
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="D53" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3" t="s">
@@ -11877,16 +11880,16 @@
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="D54" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>185</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>377</v>
@@ -11904,13 +11907,13 @@
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>188</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>16</v>
@@ -11929,16 +11932,16 @@
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="D56" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
@@ -11950,13 +11953,13 @@
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>194</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>16</v>
@@ -11975,13 +11978,13 @@
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>46</v>
@@ -11998,11 +12001,11 @@
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B59" s="3"/>
       <c r="C59" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>16</v>
@@ -12017,17 +12020,17 @@
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B60" s="3"/>
       <c r="C60" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>472</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>473</v>
@@ -12038,14 +12041,14 @@
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B61" s="3"/>
       <c r="C61" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>205</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>206</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>380</v>
@@ -12059,11 +12062,11 @@
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B62" s="3"/>
       <c r="C62" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>16</v>
@@ -12078,14 +12081,14 @@
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B63" s="3"/>
       <c r="C63" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>211</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>381</v>
@@ -12099,14 +12102,14 @@
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B64" s="3"/>
       <c r="C64" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D64" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>215</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>382</v>
@@ -12120,19 +12123,19 @@
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="C65" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>218</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>62</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>461</v>
@@ -12145,16 +12148,16 @@
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>221</v>
-      </c>
       <c r="D66" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>383</v>
@@ -12170,16 +12173,16 @@
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="C67" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="D67" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>226</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
@@ -12193,13 +12196,13 @@
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="C68" s="3" t="s">
         <v>228</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>229</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>41</v>
@@ -12214,16 +12217,16 @@
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="C69" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="C69" s="3" t="s">
-        <v>232</v>
-      </c>
       <c r="D69" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>384</v>
@@ -12237,19 +12240,19 @@
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="D70" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="D70" s="3" t="s">
-        <v>236</v>
-      </c>
       <c r="E70" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>447</v>
@@ -12262,16 +12265,16 @@
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="D71" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>240</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>372</v>
@@ -12285,16 +12288,16 @@
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="C72" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="D72" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>244</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3" t="s">
@@ -12306,16 +12309,16 @@
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="D73" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>248</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>385</v>
@@ -12329,16 +12332,16 @@
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="C74" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="D74" s="3" t="s">
         <v>251</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>252</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3" t="s">
@@ -12350,16 +12353,16 @@
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="C75" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="D75" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3" t="s">
@@ -12371,13 +12374,13 @@
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="C76" s="3" t="s">
         <v>258</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>259</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>477</v>
@@ -12392,16 +12395,16 @@
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B77" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="C77" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="D77" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3" t="s">
@@ -12438,13 +12441,13 @@
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>266</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>267</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>62</v>
@@ -12461,13 +12464,13 @@
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B80" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="C80" s="3" t="s">
         <v>269</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>270</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>62</v>
@@ -12484,16 +12487,16 @@
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="C81" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="D81" s="3" t="s">
         <v>273</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>274</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3" t="s">
@@ -12505,16 +12508,16 @@
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="C82" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="D82" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>278</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3" t="s">
@@ -12528,13 +12531,13 @@
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="C83" s="3" t="s">
         <v>280</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>281</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>36</v>
@@ -12551,13 +12554,13 @@
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B84" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="C84" s="3" t="s">
         <v>284</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>285</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>36</v>
@@ -12572,19 +12575,19 @@
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="C85" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>288</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>390</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>37</v>
+        <v>355</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>478</v>
@@ -12597,13 +12600,13 @@
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="C86" s="3" t="s">
         <v>290</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>291</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>36</v>
@@ -12643,16 +12646,16 @@
     </row>
     <row r="88" ht="14.25" customHeight="1">
       <c r="A88" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="C88" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="D88" s="3" t="s">
         <v>294</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>295</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3" t="s">
@@ -12687,13 +12690,13 @@
     </row>
     <row r="90" ht="14.25" customHeight="1">
       <c r="A90" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="C90" s="3" t="s">
         <v>297</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>298</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>420</v>
@@ -12708,13 +12711,13 @@
     </row>
     <row r="91" ht="14.25" customHeight="1">
       <c r="A91" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B91" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="C91" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>62</v>
@@ -12764,11 +12767,11 @@
       <c r="C93" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="D93" s="16" t="s">
+      <c r="D93" s="17" t="s">
         <v>395</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>447</v>
@@ -12782,17 +12785,17 @@
       <c r="I93" s="3"/>
     </row>
     <row r="94" ht="14.25" customHeight="1">
-      <c r="A94" s="8" t="s">
+      <c r="A94" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="B94" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="B94" s="8" t="s">
+      <c r="C94" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="C94" s="8" t="s">
-        <v>304</v>
-      </c>
       <c r="D94" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>404</v>
@@ -12803,17 +12806,17 @@
       <c r="I94" s="3"/>
     </row>
     <row r="95" ht="14.25" customHeight="1">
-      <c r="A95" s="8" t="s">
+      <c r="A95" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="B95" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="B95" s="8" t="s">
+      <c r="C95" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="C95" s="8" t="s">
-        <v>307</v>
-      </c>
       <c r="D95" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
@@ -12822,13 +12825,13 @@
       <c r="I95" s="3"/>
     </row>
     <row r="96" ht="14.25" customHeight="1">
-      <c r="A96" s="8" t="s">
+      <c r="A96" s="9" t="s">
         <v>405</v>
       </c>
-      <c r="B96" s="8" t="s">
+      <c r="B96" s="9" t="s">
         <v>406</v>
       </c>
-      <c r="C96" s="8" t="s">
+      <c r="C96" s="9" t="s">
         <v>407</v>
       </c>
       <c r="D96" s="3" t="s">
@@ -12841,17 +12844,17 @@
       <c r="I96" s="3"/>
     </row>
     <row r="97" ht="14.25" customHeight="1">
-      <c r="A97" s="8" t="s">
+      <c r="A97" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="B97" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="B97" s="8" t="s">
+      <c r="C97" s="9" t="s">
         <v>309</v>
       </c>
-      <c r="C97" s="8" t="s">
+      <c r="D97" s="3" t="s">
         <v>310</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>311</v>
       </c>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
@@ -12860,17 +12863,17 @@
       <c r="I97" s="3"/>
     </row>
     <row r="98" ht="14.25" customHeight="1">
-      <c r="A98" s="8" t="s">
+      <c r="A98" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="B98" s="9" t="s">
         <v>312</v>
       </c>
-      <c r="B98" s="8" t="s">
+      <c r="C98" s="9" t="s">
         <v>313</v>
       </c>
-      <c r="C98" s="8" t="s">
-        <v>314</v>
-      </c>
       <c r="D98" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
@@ -12879,13 +12882,13 @@
       <c r="I98" s="3"/>
     </row>
     <row r="99" ht="14.25" customHeight="1">
-      <c r="A99" s="8" t="s">
+      <c r="A99" s="9" t="s">
         <v>408</v>
       </c>
-      <c r="B99" s="8" t="s">
+      <c r="B99" s="9" t="s">
         <v>409</v>
       </c>
-      <c r="C99" s="8" t="s">
+      <c r="C99" s="9" t="s">
         <v>410</v>
       </c>
       <c r="D99" s="3" t="s">
@@ -12898,12 +12901,12 @@
       <c r="I99" s="3"/>
     </row>
     <row r="100" ht="14.25" customHeight="1">
-      <c r="A100" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="B100" s="8"/>
-      <c r="C100" s="8" t="s">
-        <v>317</v>
+      <c r="A100" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="B100" s="9"/>
+      <c r="C100" s="9" t="s">
+        <v>316</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>487</v>
@@ -12915,12 +12918,12 @@
       <c r="I100" s="3"/>
     </row>
     <row r="101" ht="14.25" customHeight="1">
-      <c r="A101" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="B101" s="8"/>
-      <c r="C101" s="8" t="s">
-        <v>320</v>
+      <c r="A101" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="B101" s="9"/>
+      <c r="C101" s="9" t="s">
+        <v>319</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>395</v>
@@ -12932,11 +12935,11 @@
       <c r="I101" s="3"/>
     </row>
     <row r="102" ht="14.25" customHeight="1">
-      <c r="A102" s="8" t="s">
+      <c r="A102" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="B102" s="8"/>
-      <c r="C102" s="8" t="s">
+      <c r="B102" s="9"/>
+      <c r="C102" s="9" t="s">
         <v>412</v>
       </c>
       <c r="D102" s="3" t="s">
@@ -12951,13 +12954,13 @@
       <c r="I102" s="3"/>
     </row>
     <row r="103" ht="14.25" customHeight="1">
-      <c r="A103" s="8" t="s">
+      <c r="A103" s="9" t="s">
         <v>488</v>
       </c>
-      <c r="B103" s="8" t="s">
+      <c r="B103" s="9" t="s">
         <v>415</v>
       </c>
-      <c r="C103" s="8" t="s">
+      <c r="C103" s="9" t="s">
         <v>416</v>
       </c>
       <c r="D103" s="3" t="s">
@@ -12970,20 +12973,20 @@
       <c r="I103" s="3"/>
     </row>
     <row r="104" ht="14.25" customHeight="1">
-      <c r="A104" s="8" t="s">
+      <c r="A104" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="B104" s="9" t="s">
         <v>321</v>
       </c>
-      <c r="B104" s="8" t="s">
+      <c r="C104" s="9" t="s">
         <v>322</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>323</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>489</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
@@ -12991,13 +12994,13 @@
       <c r="I104" s="3"/>
     </row>
     <row r="105" ht="14.25" customHeight="1">
-      <c r="A105" s="8" t="s">
+      <c r="A105" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="B105" s="8" t="s">
+      <c r="B105" s="9" t="s">
         <v>418</v>
       </c>
-      <c r="C105" s="8" t="s">
+      <c r="C105" s="9" t="s">
         <v>419</v>
       </c>
       <c r="D105" s="3" t="s">
@@ -13012,13 +13015,13 @@
       <c r="I105" s="3"/>
     </row>
     <row r="106" ht="14.25" customHeight="1">
-      <c r="A106" s="8" t="s">
+      <c r="A106" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="B106" s="8" t="s">
+      <c r="B106" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="C106" s="8" t="s">
+      <c r="C106" s="9" t="s">
         <v>424</v>
       </c>
       <c r="D106" s="3" t="s">
@@ -13031,13 +13034,13 @@
       <c r="I106" s="3"/>
     </row>
     <row r="107" ht="14.25" customHeight="1">
-      <c r="A107" s="8" t="s">
+      <c r="A107" s="9" t="s">
         <v>425</v>
       </c>
-      <c r="B107" s="8" t="s">
+      <c r="B107" s="9" t="s">
         <v>426</v>
       </c>
-      <c r="C107" s="8" t="s">
+      <c r="C107" s="9" t="s">
         <v>427</v>
       </c>
       <c r="D107" s="3" t="s">
@@ -13052,13 +13055,13 @@
       <c r="I107" s="3"/>
     </row>
     <row r="108" ht="14.25" customHeight="1">
-      <c r="A108" s="8" t="s">
+      <c r="A108" s="9" t="s">
         <v>490</v>
       </c>
-      <c r="B108" s="8" t="s">
+      <c r="B108" s="9" t="s">
         <v>491</v>
       </c>
-      <c r="C108" s="8" t="s">
+      <c r="C108" s="9" t="s">
         <v>492</v>
       </c>
       <c r="D108" s="3" t="s">
@@ -13071,20 +13074,20 @@
       <c r="I108" s="3"/>
     </row>
     <row r="109" ht="14.25" customHeight="1">
-      <c r="A109" s="8" t="s">
+      <c r="A109" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="B109" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="B109" s="8" t="s">
+      <c r="C109" s="9" t="s">
         <v>327</v>
-      </c>
-      <c r="C109" s="8" t="s">
-        <v>328</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>62</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="3"/>
@@ -13092,20 +13095,20 @@
       <c r="I109" s="3"/>
     </row>
     <row r="110" ht="14.25" customHeight="1">
-      <c r="A110" s="8" t="s">
+      <c r="A110" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="B110" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="B110" s="8" t="s">
+      <c r="C110" s="9" t="s">
         <v>330</v>
-      </c>
-      <c r="C110" s="8" t="s">
-        <v>331</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>451</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F110" s="3"/>
       <c r="G110" s="3"/>
@@ -13113,14 +13116,14 @@
       <c r="I110" s="3"/>
     </row>
     <row r="111" ht="14.25" customHeight="1">
-      <c r="A111" s="8" t="s">
+      <c r="A111" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="B111" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="B111" s="8" t="s">
+      <c r="C111" s="9" t="s">
         <v>333</v>
-      </c>
-      <c r="C111" s="8" t="s">
-        <v>334</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>62</v>
@@ -13134,14 +13137,14 @@
       <c r="I111" s="3"/>
     </row>
     <row r="112" ht="14.25" customHeight="1">
-      <c r="A112" s="8" t="s">
+      <c r="A112" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="B112" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="B112" s="8" t="s">
+      <c r="C112" s="9" t="s">
         <v>336</v>
-      </c>
-      <c r="C112" s="8" t="s">
-        <v>337</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>62</v>
@@ -13155,14 +13158,14 @@
       <c r="I112" s="3"/>
     </row>
     <row r="113" ht="14.25" customHeight="1">
-      <c r="A113" s="8" t="s">
+      <c r="A113" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="B113" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="B113" s="8" t="s">
+      <c r="C113" s="9" t="s">
         <v>339</v>
-      </c>
-      <c r="C113" s="8" t="s">
-        <v>340</v>
       </c>
       <c r="D113" s="3" t="s">
         <v>62</v>
@@ -13176,14 +13179,14 @@
       <c r="I113" s="3"/>
     </row>
     <row r="114" ht="14.25" customHeight="1">
-      <c r="A114" s="8" t="s">
+      <c r="A114" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="B114" s="9" t="s">
         <v>341</v>
       </c>
-      <c r="B114" s="8" t="s">
+      <c r="C114" s="9" t="s">
         <v>342</v>
-      </c>
-      <c r="C114" s="8" t="s">
-        <v>343</v>
       </c>
       <c r="D114" s="3" t="s">
         <v>62</v>
@@ -13197,14 +13200,14 @@
       <c r="I114" s="3"/>
     </row>
     <row r="115" ht="14.25" customHeight="1">
-      <c r="A115" s="8" t="s">
+      <c r="A115" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="B115" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="B115" s="8" t="s">
+      <c r="C115" s="9" t="s">
         <v>345</v>
-      </c>
-      <c r="C115" s="8" t="s">
-        <v>346</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>62</v>
@@ -13216,13 +13219,13 @@
       <c r="I115" s="3"/>
     </row>
     <row r="116" ht="14.25" customHeight="1">
-      <c r="A116" s="8" t="s">
+      <c r="A116" s="9" t="s">
         <v>494</v>
       </c>
-      <c r="B116" s="8" t="s">
+      <c r="B116" s="9" t="s">
         <v>495</v>
       </c>
-      <c r="C116" s="8" t="s">
+      <c r="C116" s="9" t="s">
         <v>496</v>
       </c>
       <c r="D116" s="3" t="s">
@@ -13235,13 +13238,13 @@
       <c r="I116" s="3"/>
     </row>
     <row r="117" ht="14.25" customHeight="1">
-      <c r="A117" s="8" t="s">
+      <c r="A117" s="9" t="s">
         <v>497</v>
       </c>
-      <c r="B117" s="8" t="s">
+      <c r="B117" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="C117" s="8" t="s">
+      <c r="C117" s="9" t="s">
         <v>499</v>
       </c>
       <c r="D117" s="3" t="s">
@@ -13256,13 +13259,13 @@
       <c r="I117" s="3"/>
     </row>
     <row r="118" ht="14.25" customHeight="1">
-      <c r="A118" s="8" t="s">
+      <c r="A118" s="9" t="s">
         <v>502</v>
       </c>
-      <c r="B118" s="8" t="s">
+      <c r="B118" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="C118" s="8" t="s">
+      <c r="C118" s="9" t="s">
         <v>504</v>
       </c>
       <c r="D118" s="3" t="s">
@@ -13275,13 +13278,13 @@
       <c r="I118" s="3"/>
     </row>
     <row r="119" ht="14.25" customHeight="1">
-      <c r="A119" s="8" t="s">
+      <c r="A119" s="9" t="s">
         <v>505</v>
       </c>
-      <c r="B119" s="8" t="s">
+      <c r="B119" s="9" t="s">
         <v>506</v>
       </c>
-      <c r="C119" s="8" t="s">
+      <c r="C119" s="9" t="s">
         <v>507</v>
       </c>
       <c r="D119" s="3" t="s">
@@ -13296,17 +13299,17 @@
       <c r="I119" s="3"/>
     </row>
     <row r="120" ht="14.25" customHeight="1">
-      <c r="A120" s="8" t="s">
+      <c r="A120" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="B120" s="9" t="s">
         <v>347</v>
       </c>
-      <c r="B120" s="8" t="s">
+      <c r="C120" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="C120" s="8" t="s">
+      <c r="D120" s="3" t="s">
         <v>349</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>350</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>372</v>
@@ -13317,13 +13320,13 @@
       <c r="I120" s="3"/>
     </row>
     <row r="121" ht="14.25" customHeight="1">
-      <c r="A121" s="8" t="s">
+      <c r="A121" s="9" t="s">
         <v>509</v>
       </c>
-      <c r="B121" s="8" t="s">
+      <c r="B121" s="9" t="s">
         <v>510</v>
       </c>
-      <c r="C121" s="8" t="s">
+      <c r="C121" s="9" t="s">
         <v>511</v>
       </c>
       <c r="D121" s="3" t="s">
@@ -14218,67 +14221,67 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14">
+      <c r="A3" s="15">
         <v>27.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="15" t="s">
         <v>515</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14">
+      <c r="A7" s="15">
         <v>22.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="15" t="s">
         <v>516</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14">
+      <c r="A12" s="15">
         <v>6.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="15" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14">
+      <c r="A16" s="15">
         <v>6.0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="15" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14">
+      <c r="A20" s="15">
         <v>5.0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="15" t="s">
         <v>519</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14">
+      <c r="A24" s="15">
         <v>4.0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="15" t="s">
         <v>520</v>
       </c>
     </row>
@@ -14303,7 +14306,7 @@
   <sheetData>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
@@ -14385,7 +14388,7 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
@@ -14405,7 +14408,7 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>530</v>
@@ -14414,7 +14417,7 @@
         <v>531</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>443</v>
@@ -14425,7 +14428,7 @@
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3" t="s">
@@ -14443,7 +14446,7 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3" t="s">
@@ -14483,7 +14486,7 @@
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3" t="s">
@@ -14503,7 +14506,7 @@
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3" t="s">
@@ -14523,7 +14526,7 @@
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3" t="s">
@@ -14543,13 +14546,13 @@
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>191</v>
       </c>
       <c r="D18" s="3">
         <v>1.0</v>
